--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_899_Corsica_France.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_899_Corsica_France.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R5e40a86a588444f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re47b9a1fb1c14883"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1344684162db4b0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R252af4ea9ffd4ddb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R533bf8786df44f22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R18feea95c57c41a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R81a1a7ae92da4abf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd11e1bc739fb4823"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R6f7d3b5ce81b43c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R2877f24387e84200"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3ef32b4c81b44eee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R5e7c039a23414c7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ899CommercialTable" displayName="EEZ899CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ899CommercialTable" displayName="EEZ899CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ899FunctionalTable" displayName="EEZ899FunctionalTable" ref="A1:O25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O25"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ899FunctionalTable" displayName="EEZ899FunctionalTable" ref="A1:E25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E25"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ899ValidationTable" displayName="EEZ899ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ899ValidationTable" displayName="EEZ899ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8332,7 +8286,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd929253fe6547b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9ef92e589004ae4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8342,20 +8296,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8363,714 +8307,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>5.0383127329</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>5.0383127329</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$115,A2,'Species'!$U$2:$U$115))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>649.0604119448232</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>649.0604119448232</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>61.74938780219999</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.244635974432298</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1756.4507400243785</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>61.74938780219999</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1892.0725181674095</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$115,A3,'Species'!$U$2:$U$115))</x:f>
-        <x:v>116834.31967420445</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.244635974432298</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1756.4507400243785</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>108459.7579012265</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>8374.561772977948</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0772135392428646</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.07721353924286462</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>129.90797572239998</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.0823443102384704</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>120.87717739690439</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>129.90797572239998</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>142.5771117437883</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$115,A4,'Species'!$U$2:$U$115))</x:f>
-        <x:v>18521.90397098196</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.0823443102384704</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>120.87717739690439</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>15702.90942666929</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>2818.994544312669</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.179520525000608</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.1795205250006081</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>10.977076370499999</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.484013282506751</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>304.7988208184856</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>10.977076370499999</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>348.12992000362584</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$115,A5,'Species'!$U$2:$U$115))</x:f>
-        <x:v>3821.448718735856</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.484013282506751</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>304.7988208184856</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3345.799933762861</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>475.6487849729947</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1421629488879974</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.14216294888799738</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.09999999999999999</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>251.18864315095797</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.09999999999999999</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>251.18864315095797</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$115,A6,'Species'!$U$2:$U$115))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>25.118864315095795</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.4</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>251.18864315095797</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>25.118864315095795</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>7.1799990504</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0982207138663496</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>12.537781987567563</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>7.1799990504</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>12.543183878456166</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$115,A7,'Species'!$U$2:$U$115))</x:f>
-        <x:v>90.06004833630786</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0982207138663496</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>12.537781987567563</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>90.02126276485733</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0.038785571450532075</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0004308490045495</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.00043084900454954804</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>433.84415327749997</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.313168811963725</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>205.66898840329148</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>433.84415327749997</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>467.7389617180075</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$115,A8,'Species'!$U$2:$U$115))</x:f>
-        <x:v>202925.81380144594</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.313168811963725</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>205.66898840329148</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>89228.28812926596</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>113697.52567217998</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>2.274231838982108</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>1.2742318389821083</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>787.4816739920999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6260211832528864</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>422.6892309551505</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>787.4816739920999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>877.1079078069331</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$115,A9,'Species'!$U$2:$U$115))</x:f>
-        <x:v>690706.4035115121</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6260211832528864</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>422.6892309551505</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>332860.02317099523</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>357846.38034051686</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.075065659527055</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.0750656595270551</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>13.5378618281</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.35</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>223.872113856834</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>13.5378618281</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$115,A10,'Species'!$U$2:$U$115))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>3030.7497445584904</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.35</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>3030.7497445584904</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>46.4395345936</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.8920057236520376</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>779.8403881247473</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>46.4395345936</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>785.3211338406384</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$115,A11,'Species'!$U$2:$U$115))</x:f>
-        <x:v>36469.9479620775</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.8920057236520376</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>779.8403881247473</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>36215.424681805656</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>254.52328027184558</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.007028035222785</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0070280352227849495</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>48.581622420100004</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.837978157815714</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>688.6176624892541</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>48.581622420100004</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>782.4948163393833</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$115,A12,'Species'!$U$2:$U$115))</x:f>
-        <x:v>38014.86771308542</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.837978157815714</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>688.6176624892541</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>33454.1632708648</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>4560.704442220616</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1363269619178469</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.13632696191784682</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>20.1880613759</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.386518213992408</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2435.107924452896</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>20.1880613759</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2476.962915322926</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$115,A13,'Species'!$U$2:$U$115))</x:f>
-        <x:v>50005.079360367425</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.386518213992408</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2435.107924452896</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>49160.108235795524</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>844.9711245719009</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.017188146139122</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.017188146139121844</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R649b3ec6a1034ae6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda29da58a2554ee8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9080,20 +8560,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9101,1362 +8571,478 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>32.341789116899996</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.1445574675515395</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1394.9462301918802</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>32.341789116899996</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1449.042602719736</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$115,A2,'Species'!$U$2:$U$115))</x:f>
-        <x:v>46864.6302785656</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.1445574675515395</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1394.9462301918802</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>45115.05680628043</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1749.5734722851703</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0387802564407191</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.038780256440719224</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2.1497745477</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.120983646459235</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1321.245881182347</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2.1497745477</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1337.6158427015794</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$115,A3,'Species'!$U$2:$U$115))</x:f>
-        <x:v>2875.572493240142</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.120983646459235</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1321.245881182347</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2840.3807666192674</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>35.19172662087476</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0123897919020066</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.012389791902006623</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>138.1729541797</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.347261604090828</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2224.6495396638916</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>138.1729541797</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>3068.0407631970243</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$115,A4,'Species'!$U$2:$U$115))</x:f>
-        <x:v>423920.2557946743</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.347261604090828</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2224.6495396638916</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>307386.3989098696</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>116533.85688480467</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.3791119493187927</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.37911194931879266</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>39.1858327573</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.1646784885267465</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1461.095114268864</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>39.1858327573</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1935.5543473454761</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$115,A5,'Species'!$U$2:$U$115))</x:f>
-        <x:v>75846.30894774478</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.1646784885267465</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1461.095114268864</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>57254.22879024784</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>18592.080157496937</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.3247285056551794</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.3247285056551795</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.19999999999999998</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.19999999999999998</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$115,A6,'Species'!$U$2:$U$115))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>458.17353055355494</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>458.17353055355494</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>21.3055596231</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.386146862642274</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2433.026631338302</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>21.3055596231</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2472.6523144346947</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$115,A7,'Species'!$U$2:$U$115))</x:f>
-        <x:v>52681.24131238459</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.386146862642274</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2433.026631338302</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>51836.99395856834</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>844.2473538162521</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0162865800916432</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.01628658009164328</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>27.001043307099998</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.7560100267169805</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>570.1774360256788</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>27.001043307099998</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>605.220175193517</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$115,A8,'Species'!$U$2:$U$115))</x:f>
-        <x:v>16341.576160730801</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.7560100267169805</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>570.1774360256788</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>15395.385642860592</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>946.1905178702091</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0614593580063383</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.06145935800633825</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>45.5672873209</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.038112144868221</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1091.7222079491885</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>45.5672873209</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1299.8942089290372</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$115,A9,'Species'!$U$2:$U$115))</x:f>
-        <x:v>59232.652905043455</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.038112144868221</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1091.7222079491885</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>49746.81952422801</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>9485.833380815442</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.190682207858446</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.19068220785844592</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>6.0963260234</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.218114390992726</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1652.3969740070233</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>6.0963260234</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1826.0120165259032</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$115,A10,'Species'!$U$2:$U$115))</x:f>
-        <x:v>11131.964575387974</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.218114390992726</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1652.3969740070233</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>10073.550673626429</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1058.4139017615453</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1050686035195694</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.10506860351956927</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>117.37310451389999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.096027232046173</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>124.74617327602961</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>117.37310451389999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>145.67211663577467</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$115,A11,'Species'!$U$2:$U$115))</x:f>
-        <x:v>17097.98857065181</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.096027232046173</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>124.74617327602961</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>14641.845633636502</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2456.142937015309</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1677481786430564</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.16774817864305627</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>29.1420306671</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.9259359359548784</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>843.2103641706453</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>29.1420306671</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1604.1256162426384</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$115,A12,'Species'!$U$2:$U$115))</x:f>
-        <x:v>46747.477902423656</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.9259359359548784</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>843.2103641706453</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>24572.862291477504</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>22174.61561094615</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.9024026321360565</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.9024026321360566</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.026464519199999998</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.026464519199999998</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$115,A13,'Species'!$U$2:$U$115))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>31.81735021340967</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>31.81735021340967</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>368.2875963816</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.4802345679991746</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>302.15832754879426</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>368.2875963816</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>488.6874192177086</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$115,A14,'Species'!$U$2:$U$115))</x:f>
-        <x:v>179977.51500561723</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.4802345679991746</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>302.15832754879426</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>111281.16417962963</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>68696.3508259876</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.6173223593805885</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.6173223593805885</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>394.8579515300999</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.2749412130103663</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>188.33941321512782</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>394.8579515300999</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>207.2867885854288</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$115,A15,'Species'!$U$2:$U$115))</x:f>
-        <x:v>81848.83672009532</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.2749412130103663</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>188.33941321512782</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>74367.3148945064</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>7481.5218255889195</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.1006022852405228</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.10060228524052289</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>51.0573210507</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.6818513707205307</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>480.6748182031456</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>51.0573210507</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>484.2544797583969</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$115,A16,'Species'!$U$2:$U$115))</x:f>
-        <x:v>24724.736443264173</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.6818513707205307</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>480.6748182031456</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>24541.96851398486</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>182.76792927931456</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0074471584940372</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.007447158494037147</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>152.57739637179998</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.672879151431957</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>470.84628854219926</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>152.57739637179998</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>591.6979264559582</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$115,A17,'Species'!$U$2:$U$115))</x:f>
-        <x:v>90279.72905724288</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.672879151431957</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>470.84628854219926</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>71840.50079709404</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>18439.22826014884</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.2566689827542894</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.25666898275428934</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>60.645933657</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.27758550175403</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>18.9489653551329</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>60.645933657</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>19.244026651650714</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$115,A18,'Species'!$U$2:$U$115))</x:f>
-        <x:v>1167.0719636095491</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.27758550175403</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>18.9489653551329</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>1149.1776957961813</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>17.894267813367833</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0155713671426334</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.015571367142633413</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>12.5348712085</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.9542211740149456</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>89.99557871189081</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>12.5348712085</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>113.59633271417887</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$115,A19,'Species'!$U$2:$U$115))</x:f>
-        <x:v>1423.9154003301473</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.9542211740149456</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>89.99557871189081</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>1128.0829884879756</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>295.8324118421717</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.262243482847561</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.26224348284756094</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>1.2532925194</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.40074535640925</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>251.6201149449818</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>1.2532925194</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>255.57256932876655</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$115,A20,'Species'!$U$2:$U$115))</x:f>
-        <x:v>320.30718930358097</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.40074535640925</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>251.6201149449818</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>315.3536077911138</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>4.953581512467167</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0157080223282189</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.01570802232821879</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>31.960949492100003</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.5737030871020665</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>374.7167331095855</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>31.960949492100003</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>414.40907789710536</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$115,A21,'Species'!$U$2:$U$115))</x:f>
-        <x:v>13244.907607737121</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.5737030871020665</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>374.7167331095855</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>11976.302580760179</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>1268.605026976942</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.105926267178231</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.10592626717823116</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>7.026850918099999</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.138315448696299</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>137.5040369465581</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>7.026850918099999</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>138.53893001984702</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$115,A22,'Species'!$U$2:$U$115))</x:f>
-        <x:v>973.4924076025536</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.138315448696299</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>137.5040369465581</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>966.220368260378</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>7.272039342175617</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0075262741099822</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.007526274109982269</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>10.7770763705</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.467756800927181</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>293.60050681547074</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>10.7770763705</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>312.0767704113674</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$115,A23,'Species'!$U$2:$U$115))</x:f>
-        <x:v>3363.275188182301</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.467756800927181</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>293.60050681547074</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>3164.1550843678338</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>199.12010381446726</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0629299444891935</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.06292994448919353</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>4.4305708932</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.793228863565632</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>621.1963046738246</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>4.4305708932</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>623.8537547611706</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$115,A24,'Species'!$U$2:$U$115))</x:f>
-        <x:v>2764.028287458373</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.793228863565632</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>621.1963046738246</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>2752.254266451246</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>11.774021007126976</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0042779554021033</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.004277955402103305</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>11.053682196399999</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.846487138422286</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>702.2425466010893</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>11.053682196399999</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>703.5934769357862</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$115,A25,'Species'!$U$2:$U$115))</x:f>
-        <x:v>7777.298689508273</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.846487138422286</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>702.2425466010893</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>7762.3659349190575</x:v>
       </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>14.93275458921562</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0019237375195158</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.0019237375195158629</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G25">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O25">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07d60b4553cf496c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb45fa483f5114bb2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10631,7 +9217,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10730,7 +9316,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1161094.7737815655</x:v>
+        <x:v>672221.425033969</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10744,7 +9330,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1161094.7737815655</x:v>
+        <x:v>890598.3747902303</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10758,7 +9344,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>2.3283064365386963e-10</x:v>
+        <x:v>-488873.34874759626</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10772,7 +9358,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>2.3283064365386963e-10</x:v>
+        <x:v>-270496.39899133495</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10783,9 +9369,9 @@
         <x:v>EEZ_899</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10797,47 +9383,19 @@
         <x:v>EEZ_899</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_899</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_899</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9597dd89cd754b23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a9054c737e64837"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10884,7 +9442,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
